--- a/ExcelRAddIn/Tests/Stock Market Data Analysis.xlsx
+++ b/ExcelRAddIn/Tests/Stock Market Data Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\ExcelRAddIn\ExcelRAddIn\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D1F003-7C8F-450A-925C-46594D9D66C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA1F500-A4D2-4BCB-BE9F-AE16BBABC231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{6DE01E39-80F5-4793-B19A-E999CA1A29DE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6DE01E39-80F5-4793-B19A-E999CA1A29DE}"/>
   </bookViews>
   <sheets>
     <sheet name="References" sheetId="1" r:id="rId1"/>
@@ -40,9 +40,8 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
+  <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -53,25 +52,11 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </valueMetadata>
 </metadata>
 </file>
 
@@ -282,72 +267,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>8</v>
-    <v>28</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="colOffset" t="i"/>
-    <k n="errorType" t="i"/>
-    <k n="rwOffset" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -385,7 +308,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -491,7 +414,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -633,7 +556,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -696,7 +619,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1AF659-3AA9-4245-9BF7-1FBDED3808DC}">
-  <dimension ref="B2:D14"/>
+  <dimension ref="B2:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.77734375" customWidth="1"/>
@@ -706,9 +629,9 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="D2" ca="1">_xll.RScript.Evaluate(B2)</f>
-        <v>#VALUE!</v>
+      <c r="D2" t="str" cm="1">
+        <f t="array" ref="D2">_xll.RScript.Evaluate(B2, TRUE)</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
@@ -716,63 +639,8 @@
         <v>14</v>
       </c>
       <c r="D3" t="str" cm="1">
-        <f t="array" ref="D3:D14">_xll.RScript.Evaluate(B3)</f>
-        <v>magrittr</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D4" t="str">
-        <v>quantmod</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D5" t="str">
-        <v>TTR</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D6" t="str">
-        <v>xts</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D7" t="str">
-        <v>zoo</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D8" t="str">
-        <v>stats</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D9" t="str">
-        <v>graphics</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D10" t="str">
-        <v>grDevices</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D11" t="str">
-        <v>utils</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D12" t="str">
-        <v>datasets</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D13" t="str">
-        <v>methods</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D14" t="str">
-        <v>base</v>
+        <f t="array" ref="D3">_xll.RScript.Evaluate(B3, TRUE)</f>
+        <v>OK</v>
       </c>
     </row>
   </sheetData>
@@ -782,7 +650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7C1B5B-F730-4FDC-989B-9FE7E06D0672}">
-  <dimension ref="B2:M17"/>
+  <dimension ref="B2:AS17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -791,7 +659,7 @@
     <col min="7" max="7" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>16</v>
       </c>
@@ -808,20 +676,62 @@
         <v>R.version</v>
       </c>
       <c r="G2" t="str" cm="1">
-        <f t="array" ref="G2">_xll.RScript.Evaluate($D$2&amp;"$"&amp;F2&amp;"")</f>
-        <v>List of 15 objects.</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+        <f t="array" ref="G2:U2">TRANSPOSE(_xll.RScript.Evaluate($D$2&amp;"$"&amp;F2&amp;""))</f>
+        <v>platform</v>
+      </c>
+      <c r="H2" t="str">
+        <v>arch</v>
+      </c>
+      <c r="I2" t="str">
+        <v>os</v>
+      </c>
+      <c r="J2" t="str">
+        <v>crt</v>
+      </c>
+      <c r="K2" t="str">
+        <v>system</v>
+      </c>
+      <c r="L2" t="str">
+        <v>status</v>
+      </c>
+      <c r="M2" t="str">
+        <v>major</v>
+      </c>
+      <c r="N2" t="str">
+        <v>minor</v>
+      </c>
+      <c r="O2" t="str">
+        <v>year</v>
+      </c>
+      <c r="P2" t="str">
+        <v>month</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>day</v>
+      </c>
+      <c r="R2" t="str">
+        <v>svn rev</v>
+      </c>
+      <c r="S2" t="str">
+        <v>language</v>
+      </c>
+      <c r="T2" t="str">
+        <v>version.string</v>
+      </c>
+      <c r="U2" t="str">
+        <v>nickname</v>
+      </c>
+    </row>
+    <row r="3" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F3" t="str">
         <v>platform</v>
       </c>
       <c r="G3" t="str" cm="1">
         <f t="array" ref="G3">_xll.RScript.Evaluate($D$2&amp;"$"&amp;F3&amp;"")</f>
-        <v>x86_64-w64-mingw32/x64 (64-bit)</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+        <v>x86_64-w64-mingw32/x64</v>
+      </c>
+    </row>
+    <row r="4" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F4" t="str">
         <v>locale</v>
       </c>
@@ -830,7 +740,7 @@
         <v>LC_COLLATE=English_United Kingdom.1252;LC_CTYPE=English_United Kingdom.1252;LC_MONETARY=English_United Kingdom.1252;LC_NUMERIC=C;LC_TIME=English_United Kingdom.1252</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F5" t="str">
         <v>tzone</v>
       </c>
@@ -839,7 +749,7 @@
         <v>Europe/Madrid</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F6" t="str">
         <v>tzcode_type</v>
       </c>
@@ -848,16 +758,16 @@
         <v>internal</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F7" t="str">
         <v>running</v>
       </c>
       <c r="G7" t="str" cm="1">
         <f t="array" ref="G7">_xll.RScript.Evaluate($D$2&amp;"$"&amp;F7&amp;"")</f>
-        <v>Windows 11 x64 (build 22621)</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+        <v>Windows 11 x64 (build 26200)</v>
+      </c>
+    </row>
+    <row r="8" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F8" t="str">
         <v>RNGkind</v>
       </c>
@@ -872,7 +782,7 @@
         <v>Rejection</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F9" t="str">
         <v>basePkgs</v>
       </c>
@@ -899,25 +809,190 @@
         <v>base</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F10" t="str">
         <v>otherPkgs</v>
       </c>
       <c r="G10" t="str" cm="1">
-        <f t="array" ref="G10">TRANSPOSE(_xll.RScript.Evaluate($D$2&amp;"$"&amp;F10&amp;""))</f>
-        <v>List of 5 objects.</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+        <f t="array" ref="G10:X10">TRANSPOSE(_xll.RScript.Evaluate($D$2&amp;"$"&amp;F10&amp;""))</f>
+        <v>magrittr</v>
+      </c>
+      <c r="H10" t="str">
+        <v>quantmod</v>
+      </c>
+      <c r="I10" t="str">
+        <v>TTR</v>
+      </c>
+      <c r="J10" t="str">
+        <v>xts</v>
+      </c>
+      <c r="K10" t="str">
+        <v>zoo</v>
+      </c>
+      <c r="L10" t="str">
+        <v>reticulate</v>
+      </c>
+      <c r="M10" t="str">
+        <v>ggthemes</v>
+      </c>
+      <c r="N10" t="str">
+        <v>forecast</v>
+      </c>
+      <c r="O10" t="str">
+        <v>lubridate</v>
+      </c>
+      <c r="P10" t="str">
+        <v>forcats</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>stringr</v>
+      </c>
+      <c r="R10" t="str">
+        <v>dplyr</v>
+      </c>
+      <c r="S10" t="str">
+        <v>purrr</v>
+      </c>
+      <c r="T10" t="str">
+        <v>readr</v>
+      </c>
+      <c r="U10" t="str">
+        <v>tidyr</v>
+      </c>
+      <c r="V10" t="str">
+        <v>tibble</v>
+      </c>
+      <c r="W10" t="str">
+        <v>ggplot2</v>
+      </c>
+      <c r="X10" t="str">
+        <v>tidyverse</v>
+      </c>
+    </row>
+    <row r="11" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F11" t="str">
         <v>loadedOnly</v>
       </c>
       <c r="G11" t="str" cm="1">
-        <f t="array" ref="G11">TRANSPOSE(_xll.RScript.Evaluate($D$2&amp;"$"&amp;F11&amp;""))</f>
-        <v>List of 5 objects.</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+        <f t="array" ref="G11:AS11">TRANSPOSE(_xll.RScript.Evaluate($D$2&amp;"$"&amp;F11&amp;""))</f>
+        <v>generics</v>
+      </c>
+      <c r="H11" t="str">
+        <v>stringi</v>
+      </c>
+      <c r="I11" t="str">
+        <v>lattice</v>
+      </c>
+      <c r="J11" t="str">
+        <v>hms</v>
+      </c>
+      <c r="K11" t="str">
+        <v>grid</v>
+      </c>
+      <c r="L11" t="str">
+        <v>timechange</v>
+      </c>
+      <c r="M11" t="str">
+        <v>RColorBrewer</v>
+      </c>
+      <c r="N11" t="str">
+        <v>jsonlite</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Matrix</v>
+      </c>
+      <c r="P11" t="str">
+        <v>nnet</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>scales</v>
+      </c>
+      <c r="R11" t="str">
+        <v>cli</v>
+      </c>
+      <c r="S11" t="str">
+        <v>rlang</v>
+      </c>
+      <c r="T11" t="str">
+        <v>withr</v>
+      </c>
+      <c r="U11" t="str">
+        <v>tools</v>
+      </c>
+      <c r="V11" t="str">
+        <v>parallel</v>
+      </c>
+      <c r="W11" t="str">
+        <v>tzdb</v>
+      </c>
+      <c r="X11" t="str">
+        <v>colorspace</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>curl</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>png</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>vctrs</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>R6</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>lifecycle</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>tseries</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>pkgconfig</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>urca</v>
+      </c>
+      <c r="AG11" t="str">
+        <v>pillar</v>
+      </c>
+      <c r="AH11" t="str">
+        <v>gtable</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>glue</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v>Rcpp</v>
+      </c>
+      <c r="AK11" t="str">
+        <v>lmtest</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>tidyselect</v>
+      </c>
+      <c r="AM11" t="str">
+        <v>farver</v>
+      </c>
+      <c r="AN11" t="str">
+        <v>nlme</v>
+      </c>
+      <c r="AO11" t="str">
+        <v>timeDate</v>
+      </c>
+      <c r="AP11" t="str">
+        <v>fracdiff</v>
+      </c>
+      <c r="AQ11" t="str">
+        <v>compiler</v>
+      </c>
+      <c r="AR11" t="str">
+        <v>S7</v>
+      </c>
+      <c r="AS11" t="str">
+        <v>quadprog</v>
+      </c>
+    </row>
+    <row r="12" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F12" t="str">
         <v>matprod</v>
       </c>
@@ -926,7 +1001,7 @@
         <v>default</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F13" t="str">
         <v>BLAS</v>
       </c>
@@ -935,7 +1010,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F14" t="str">
         <v>LAPACK</v>
       </c>
@@ -944,16 +1019,16 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F15" t="str">
         <v>LA_version</v>
       </c>
       <c r="G15" t="str" cm="1">
         <f t="array" ref="G15">TRANSPOSE(_xll.RScript.Evaluate($D$2&amp;"$"&amp;F15&amp;""))</f>
-        <v>3.11.0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+        <v>3.12.1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:45" x14ac:dyDescent="0.3">
       <c r="F16" t="str">
         <v>system.codepage</v>
       </c>
@@ -1088,15 +1163,15 @@
       <c r="I10" s="4">
         <v>1</v>
       </c>
-      <c r="K10" t="e" cm="1">
+      <c r="K10" t="str" cm="1">
         <f t="array" ref="K10:M198">_xll.RScript.Evaluate(F11)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L10" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="M10" t="e">
-        <v>#NUM!</v>
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
